--- a/course-design-2/outputs/tables/ch4/28_recruitment_episode_identification.xlsx
+++ b/course-design-2/outputs/tables/ch4/28_recruitment_episode_identification.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_QA十项" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_多周期岗位分布" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_周期异常清单" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_三档口径汇总" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_三档统计范围汇总" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/course-design-2/outputs/tables/ch4/28_recruitment_episode_identification.xlsx
+++ b/course-design-2/outputs/tables/ch4/28_recruitment_episode_identification.xlsx
@@ -459,7 +459,6 @@
       <c r="B2" t="n">
         <v>20556</v>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -470,7 +469,6 @@
       <c r="B3" t="n">
         <v>17144</v>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -481,7 +479,6 @@
       <c r="B4" t="n">
         <v>20554</v>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -492,7 +489,6 @@
       <c r="B5" t="n">
         <v>20142</v>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -503,7 +499,6 @@
       <c r="B6" t="n">
         <v>14745</v>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -514,7 +509,6 @@
       <c r="B7" t="n">
         <v>2399</v>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -525,7 +519,6 @@
       <c r="B8" t="n">
         <v>10</v>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -538,7 +531,6 @@
           <t>2 / 532 / 2877</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -551,7 +543,6 @@
           <t>{"first": 17142, "conflict": 2877, "reopened": 534, "uncertain": 3}</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -564,7 +555,6 @@
           <t>{"high（起止完整且无冲突）": 17265, "medium（时间冲突）": 2877, "low（起止倒置）": 412, "low（起止缺失）": 2}</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -575,7 +565,6 @@
       <c r="B12" t="n">
         <v>985</v>
       </c>
-      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -586,7 +575,6 @@
       <c r="B13" t="n">
         <v>21588</v>
       </c>
-      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -597,7 +585,6 @@
       <c r="B14" t="n">
         <v>17584</v>
       </c>
-      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1469,13 +1456,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -1631,13 +1616,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -1681,13 +1664,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -1731,13 +1712,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -1781,13 +1760,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -1831,13 +1808,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -1881,13 +1856,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -1931,13 +1904,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -1981,13 +1952,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -2087,13 +2056,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -2249,13 +2216,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -2523,13 +2488,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -2573,13 +2536,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -2847,13 +2808,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -2897,13 +2856,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -3171,13 +3128,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -3221,13 +3176,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -3271,13 +3224,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -3433,13 +3384,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -3539,13 +3488,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -3589,13 +3536,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -3639,13 +3584,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -4137,13 +4080,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -4243,13 +4184,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -4349,13 +4288,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -4679,13 +4616,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -4729,13 +4664,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -4891,13 +4824,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -5109,13 +5040,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -5159,13 +5088,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -5209,13 +5136,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -5259,13 +5184,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -5477,13 +5400,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -5527,13 +5448,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -5577,13 +5496,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -5683,13 +5600,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -6013,13 +5928,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -6063,13 +5976,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -6169,13 +6080,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -6219,13 +6128,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -6269,13 +6176,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -6319,13 +6224,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -6649,13 +6552,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -6755,13 +6656,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -7029,13 +6928,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -7079,13 +6976,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -7129,13 +7024,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -7179,13 +7072,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -7285,13 +7176,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -7335,13 +7224,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -7385,13 +7272,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -7435,13 +7320,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -7485,13 +7368,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -7535,13 +7416,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -7585,13 +7464,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -7635,13 +7512,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -7685,13 +7560,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -7735,13 +7608,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -7785,13 +7656,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -7891,13 +7760,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -7941,13 +7808,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -7991,13 +7856,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -8041,13 +7904,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -8203,13 +8064,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -8589,13 +8448,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -8695,13 +8552,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -8745,13 +8600,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -8795,13 +8648,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -8845,13 +8696,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -8895,13 +8744,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -8945,13 +8792,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -8995,13 +8840,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -9157,13 +9000,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -9207,13 +9048,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -9257,13 +9096,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -9363,13 +9200,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -9469,13 +9304,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -9519,13 +9352,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -9569,13 +9400,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -9619,13 +9448,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -9725,13 +9552,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -9775,13 +9600,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -9937,13 +9760,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -9987,13 +9808,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -10205,13 +10024,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -10255,13 +10072,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -10305,13 +10120,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -10355,13 +10168,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -10461,13 +10272,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -10567,13 +10376,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -10673,13 +10480,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -11003,13 +10808,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -11109,13 +10912,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -11159,13 +10960,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -11209,13 +11008,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -11371,13 +11168,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -11533,13 +11328,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -11583,13 +11376,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -11745,13 +11536,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -11795,13 +11584,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -11901,13 +11688,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -11951,13 +11736,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -12113,13 +11896,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -12163,13 +11944,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -12269,13 +12048,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -12319,13 +12096,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -12481,13 +12256,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -12531,13 +12304,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -12637,13 +12408,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -13023,13 +12792,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -13129,13 +12896,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -13179,13 +12944,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -13509,13 +13272,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -13559,13 +13320,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -13609,13 +13368,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -13659,13 +13416,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -13709,13 +13464,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -13815,13 +13568,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -13865,13 +13616,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -13915,13 +13664,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -14021,13 +13768,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -14351,13 +14096,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -14625,13 +14368,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -14675,13 +14416,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -14781,13 +14520,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -14831,13 +14568,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -14881,13 +14616,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -14931,13 +14664,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -14981,13 +14712,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -15087,13 +14816,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -15193,13 +14920,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -15411,13 +15136,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -15461,13 +15184,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -15511,13 +15232,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -15617,13 +15336,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -15667,13 +15384,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -15717,13 +15432,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -15767,13 +15480,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -15817,13 +15528,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -15867,13 +15576,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -16141,13 +15848,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr"/>
       <c r="I279" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -16191,13 +15896,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -16241,13 +15944,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr"/>
       <c r="I281" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -16291,13 +15992,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -16341,13 +16040,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -16503,13 +16200,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -16609,13 +16304,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -16659,13 +16352,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -16765,13 +16456,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -16815,13 +16504,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -16865,13 +16552,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -16915,13 +16600,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -16965,13 +16648,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -17295,13 +16976,11 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
           <t>high（起止完整且无冲突）</t>
@@ -17330,7 +17009,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>口径</t>
+          <t>统计范围</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
